--- a/public/template-transazioni-en.xlsx
+++ b/public/template-transazioni-en.xlsx
@@ -436,7 +436,7 @@
         <v>Withheld tax</v>
       </c>
       <c r="I1" t="str">
-        <v>Container</v>
+        <v>Group</v>
       </c>
     </row>
     <row r="2">
